--- a/data/stb_metadata.xlsx
+++ b/data/stb_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/innovation_hub/InnovationHubDashboard/inst/app/metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/innovation_hub/InnovationHubDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_6D68FDCE8F79A89360642C52EAAAD23310C181F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146F2A14-2170-4334-86CD-DF32A2FEF28D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_6D68FDCE8F79A89360642C52EAAAD23310C181F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA81AA01-A70C-4BE2-8BD0-0E7AF8FC3DE0}"/>
   <bookViews>
-    <workbookView xWindow="53880" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
